--- a/quote_automation/assets/base_quote_template.xlsx
+++ b/quote_automation/assets/base_quote_template.xlsx
@@ -758,7 +758,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1071,6 +1071,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2235,12 +2241,12 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="B2" s="81" t="n"/>
+      <c r="B2" s="118" t="n"/>
       <c r="F2" s="19" t="n"/>
       <c r="G2" s="19" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" thickBot="1">
-      <c r="B3" s="82" t="n"/>
+      <c r="B3" s="119" t="n"/>
       <c r="C3" s="90" t="n"/>
       <c r="D3" s="90" t="n"/>
       <c r="H3" s="91">
@@ -2502,7 +2508,7 @@
     <row r="23" hidden="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>③</t>
         </is>
       </c>
       <c r="C23" s="57" t="n"/>

--- a/quote_automation/assets/base_quote_template.xlsx
+++ b/quote_automation/assets/base_quote_template.xlsx
@@ -9,7 +9,7 @@
     <sheet name="見積書" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'見積書'!$A$1:$J$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'見積書'!$A$1:$J$70</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -758,7 +758,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1076,6 +1076,16 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1455,7 +1465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:Q46"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3.08984375" customWidth="1" style="1" min="1" max="1"/>
@@ -2287,7 +2297,7 @@
         </is>
       </c>
       <c r="D8" s="38">
-        <f>G26</f>
+        <f>G54</f>
         <v/>
       </c>
       <c r="E8" s="22" t="n"/>
@@ -2434,6 +2444,9 @@
       </c>
       <c r="H19" s="105" t="n"/>
       <c r="I19" s="96" t="n"/>
+      <c r="J19" s="120" t="n"/>
+      <c r="K19" s="120" t="n"/>
+      <c r="L19" s="120" t="n"/>
       <c r="M19" s="41" t="n">
         <v>1</v>
       </c>
@@ -2442,6 +2455,7 @@
         <f>M19*N19</f>
         <v/>
       </c>
+      <c r="P19" s="120" t="n"/>
       <c r="Q19" s="26">
         <f>G19-O19</f>
         <v/>
@@ -2456,9 +2470,13 @@
       <c r="G20" s="108" t="n"/>
       <c r="H20" s="109" t="n"/>
       <c r="I20" s="110" t="n"/>
+      <c r="J20" s="120" t="n"/>
+      <c r="K20" s="120" t="n"/>
+      <c r="L20" s="120" t="n"/>
       <c r="M20" s="41" t="n"/>
       <c r="N20" s="41" t="n"/>
       <c r="O20" s="41" t="n"/>
+      <c r="P20" s="120" t="n"/>
       <c r="Q20" s="26" t="n"/>
     </row>
     <row r="21" hidden="1">
@@ -2480,12 +2498,16 @@
       </c>
       <c r="H21" s="112" t="n"/>
       <c r="I21" s="113" t="n"/>
+      <c r="J21" s="120" t="n"/>
+      <c r="K21" s="120" t="n"/>
+      <c r="L21" s="120" t="n"/>
       <c r="M21" s="41" t="n"/>
       <c r="N21" s="41" t="n"/>
       <c r="O21" s="41">
         <f>M21*N21</f>
         <v/>
       </c>
+      <c r="P21" s="120" t="n"/>
       <c r="Q21" s="26">
         <f>G21-O21</f>
         <v/>
@@ -2500,9 +2522,13 @@
       <c r="G22" s="108" t="n"/>
       <c r="H22" s="109" t="n"/>
       <c r="I22" s="110" t="n"/>
+      <c r="J22" s="120" t="n"/>
+      <c r="K22" s="120" t="n"/>
+      <c r="L22" s="120" t="n"/>
       <c r="M22" s="41" t="n"/>
       <c r="N22" s="41" t="n"/>
       <c r="O22" s="41" t="n"/>
+      <c r="P22" s="120" t="n"/>
       <c r="Q22" s="26" t="n"/>
     </row>
     <row r="23" hidden="1">
@@ -2524,12 +2550,16 @@
       </c>
       <c r="H23" s="112" t="n"/>
       <c r="I23" s="113" t="n"/>
+      <c r="J23" s="120" t="n"/>
+      <c r="K23" s="120" t="n"/>
+      <c r="L23" s="120" t="n"/>
       <c r="M23" s="41" t="n"/>
       <c r="N23" s="41" t="n"/>
       <c r="O23" s="41">
         <f>M23*N23</f>
         <v/>
       </c>
+      <c r="P23" s="120" t="n"/>
       <c r="Q23" s="26">
         <f>G23-O23</f>
         <v/>
@@ -2544,9 +2574,13 @@
       <c r="G24" s="108" t="n"/>
       <c r="H24" s="109" t="n"/>
       <c r="I24" s="110" t="n"/>
+      <c r="J24" s="120" t="n"/>
+      <c r="K24" s="120" t="n"/>
+      <c r="L24" s="120" t="n"/>
       <c r="M24" s="41" t="n"/>
       <c r="N24" s="41" t="n"/>
       <c r="O24" s="41" t="n"/>
+      <c r="P24" s="120" t="n"/>
       <c r="Q24" s="26">
         <f>G24-O24</f>
         <v/>
@@ -2555,304 +2589,1125 @@
     <row r="25" hidden="1">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="C25" s="45" t="inlineStr">
+          <t>④</t>
+        </is>
+      </c>
+      <c r="C25" s="57" t="n"/>
+      <c r="D25" s="111" t="n"/>
+      <c r="E25" s="121" t="n"/>
+      <c r="F25" s="121">
+        <f>ROUNDUP(N25*$M$17,-3)</f>
+        <v/>
+      </c>
+      <c r="G25" s="121">
+        <f>E25*F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="112" t="n"/>
+      <c r="I25" s="113" t="n"/>
+      <c r="J25" s="120" t="n"/>
+      <c r="K25" s="120" t="n"/>
+      <c r="L25" s="120" t="n"/>
+      <c r="M25" s="122" t="n"/>
+      <c r="N25" s="122" t="n"/>
+      <c r="O25" s="122">
+        <f>M25*N25</f>
+        <v/>
+      </c>
+      <c r="P25" s="120" t="n"/>
+      <c r="Q25" s="123">
+        <f>G25-O25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" hidden="1" ht="13.75" customHeight="1" thickBot="1">
+      <c r="B26" s="97" t="n"/>
+      <c r="C26" s="109" t="n"/>
+      <c r="D26" s="99" t="n"/>
+      <c r="E26" s="108" t="n"/>
+      <c r="F26" s="108" t="n"/>
+      <c r="G26" s="108" t="n"/>
+      <c r="H26" s="109" t="n"/>
+      <c r="I26" s="110" t="n"/>
+      <c r="J26" s="120" t="n"/>
+      <c r="K26" s="120" t="n"/>
+      <c r="L26" s="120" t="n"/>
+      <c r="M26" s="122" t="n"/>
+      <c r="N26" s="122" t="n"/>
+      <c r="O26" s="122" t="n"/>
+      <c r="P26" s="120" t="n"/>
+      <c r="Q26" s="123" t="n"/>
+    </row>
+    <row r="27" hidden="1" ht="16" customHeight="1" thickBot="1" thickTop="1">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="C27" s="57" t="n"/>
+      <c r="D27" s="111" t="n"/>
+      <c r="E27" s="121" t="n"/>
+      <c r="F27" s="121">
+        <f>ROUNDUP(N27*$M$17,-3)</f>
+        <v/>
+      </c>
+      <c r="G27" s="121">
+        <f>E27*F27</f>
+        <v/>
+      </c>
+      <c r="H27" s="112" t="n"/>
+      <c r="I27" s="113" t="n"/>
+      <c r="J27" s="120" t="n"/>
+      <c r="K27" s="120" t="n"/>
+      <c r="L27" s="120" t="n"/>
+      <c r="M27" s="122" t="n"/>
+      <c r="N27" s="122" t="n"/>
+      <c r="O27" s="122">
+        <f>M27*N27</f>
+        <v/>
+      </c>
+      <c r="P27" s="120" t="n"/>
+      <c r="Q27" s="123">
+        <f>G27-O27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" hidden="1" ht="16" customHeight="1">
+      <c r="B28" s="97" t="n"/>
+      <c r="C28" s="109" t="n"/>
+      <c r="D28" s="99" t="n"/>
+      <c r="E28" s="108" t="n"/>
+      <c r="F28" s="108" t="n"/>
+      <c r="G28" s="108" t="n"/>
+      <c r="H28" s="109" t="n"/>
+      <c r="I28" s="110" t="n"/>
+      <c r="J28" s="120" t="n"/>
+      <c r="K28" s="120" t="n"/>
+      <c r="L28" s="120" t="n"/>
+      <c r="M28" s="122" t="n"/>
+      <c r="N28" s="122" t="n"/>
+      <c r="O28" s="122" t="n"/>
+      <c r="P28" s="120" t="n"/>
+      <c r="Q28" s="123" t="n"/>
+    </row>
+    <row r="29" hidden="1" ht="16" customHeight="1">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="C29" s="57" t="n"/>
+      <c r="D29" s="111" t="n"/>
+      <c r="E29" s="121" t="n"/>
+      <c r="F29" s="121">
+        <f>ROUNDUP(N29*$M$17,-3)</f>
+        <v/>
+      </c>
+      <c r="G29" s="121">
+        <f>E29*F29</f>
+        <v/>
+      </c>
+      <c r="H29" s="112" t="n"/>
+      <c r="I29" s="113" t="n"/>
+      <c r="J29" s="120" t="n"/>
+      <c r="K29" s="120" t="n"/>
+      <c r="L29" s="120" t="n"/>
+      <c r="M29" s="122" t="n"/>
+      <c r="N29" s="122" t="n"/>
+      <c r="O29" s="122">
+        <f>M29*N29</f>
+        <v/>
+      </c>
+      <c r="P29" s="120" t="n"/>
+      <c r="Q29" s="123">
+        <f>G29-O29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" hidden="1" ht="16" customHeight="1">
+      <c r="B30" s="97" t="n"/>
+      <c r="C30" s="109" t="n"/>
+      <c r="D30" s="99" t="n"/>
+      <c r="E30" s="108" t="n"/>
+      <c r="F30" s="108" t="n"/>
+      <c r="G30" s="108" t="n"/>
+      <c r="H30" s="109" t="n"/>
+      <c r="I30" s="110" t="n"/>
+      <c r="J30" s="120" t="n"/>
+      <c r="K30" s="120" t="n"/>
+      <c r="L30" s="120" t="n"/>
+      <c r="M30" s="122" t="n"/>
+      <c r="N30" s="122" t="n"/>
+      <c r="O30" s="122" t="n"/>
+      <c r="P30" s="120" t="n"/>
+      <c r="Q30" s="123" t="n"/>
+    </row>
+    <row r="31" hidden="1" ht="16.25" customHeight="1" thickBot="1">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>⑦</t>
+        </is>
+      </c>
+      <c r="C31" s="57" t="n"/>
+      <c r="D31" s="111" t="n"/>
+      <c r="E31" s="121" t="n"/>
+      <c r="F31" s="121">
+        <f>ROUNDUP(N31*$M$17,-3)</f>
+        <v/>
+      </c>
+      <c r="G31" s="121">
+        <f>E31*F31</f>
+        <v/>
+      </c>
+      <c r="H31" s="112" t="n"/>
+      <c r="I31" s="113" t="n"/>
+      <c r="J31" s="120" t="n"/>
+      <c r="K31" s="120" t="n"/>
+      <c r="L31" s="120" t="n"/>
+      <c r="M31" s="122" t="n"/>
+      <c r="N31" s="122" t="n"/>
+      <c r="O31" s="122">
+        <f>M31*N31</f>
+        <v/>
+      </c>
+      <c r="P31" s="120" t="n"/>
+      <c r="Q31" s="123">
+        <f>G31-O31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" hidden="1" ht="16.25" customHeight="1" thickBot="1">
+      <c r="B32" s="97" t="n"/>
+      <c r="C32" s="109" t="n"/>
+      <c r="D32" s="99" t="n"/>
+      <c r="E32" s="108" t="n"/>
+      <c r="F32" s="108" t="n"/>
+      <c r="G32" s="108" t="n"/>
+      <c r="H32" s="109" t="n"/>
+      <c r="I32" s="110" t="n"/>
+      <c r="J32" s="120" t="n"/>
+      <c r="K32" s="120" t="n"/>
+      <c r="L32" s="120" t="n"/>
+      <c r="M32" s="122" t="n"/>
+      <c r="N32" s="122" t="n"/>
+      <c r="O32" s="122" t="n"/>
+      <c r="P32" s="120" t="n"/>
+      <c r="Q32" s="123" t="n"/>
+    </row>
+    <row r="33" hidden="1" ht="16" customHeight="1">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>⑧</t>
+        </is>
+      </c>
+      <c r="C33" s="57" t="n"/>
+      <c r="D33" s="111" t="n"/>
+      <c r="E33" s="121" t="n"/>
+      <c r="F33" s="121">
+        <f>ROUNDUP(N33*$M$17,-3)</f>
+        <v/>
+      </c>
+      <c r="G33" s="121">
+        <f>E33*F33</f>
+        <v/>
+      </c>
+      <c r="H33" s="112" t="n"/>
+      <c r="I33" s="113" t="n"/>
+      <c r="J33" s="120" t="n"/>
+      <c r="K33" s="120" t="n"/>
+      <c r="L33" s="120" t="n"/>
+      <c r="M33" s="122" t="n"/>
+      <c r="N33" s="122" t="n"/>
+      <c r="O33" s="122">
+        <f>M33*N33</f>
+        <v/>
+      </c>
+      <c r="P33" s="120" t="n"/>
+      <c r="Q33" s="123">
+        <f>G33-O33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" hidden="1" ht="16" customHeight="1">
+      <c r="B34" s="97" t="n"/>
+      <c r="C34" s="109" t="n"/>
+      <c r="D34" s="99" t="n"/>
+      <c r="E34" s="108" t="n"/>
+      <c r="F34" s="108" t="n"/>
+      <c r="G34" s="108" t="n"/>
+      <c r="H34" s="109" t="n"/>
+      <c r="I34" s="110" t="n"/>
+      <c r="J34" s="120" t="n"/>
+      <c r="K34" s="120" t="n"/>
+      <c r="L34" s="120" t="n"/>
+      <c r="M34" s="122" t="n"/>
+      <c r="N34" s="122" t="n"/>
+      <c r="O34" s="122" t="n"/>
+      <c r="P34" s="120" t="n"/>
+      <c r="Q34" s="123" t="n"/>
+    </row>
+    <row r="35" hidden="1" ht="16" customHeight="1">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>⑨</t>
+        </is>
+      </c>
+      <c r="C35" s="57" t="n"/>
+      <c r="D35" s="111" t="n"/>
+      <c r="E35" s="121" t="n"/>
+      <c r="F35" s="121">
+        <f>ROUNDUP(N35*$M$17,-3)</f>
+        <v/>
+      </c>
+      <c r="G35" s="121">
+        <f>E35*F35</f>
+        <v/>
+      </c>
+      <c r="H35" s="112" t="n"/>
+      <c r="I35" s="113" t="n"/>
+      <c r="J35" s="120" t="n"/>
+      <c r="K35" s="120" t="n"/>
+      <c r="L35" s="120" t="n"/>
+      <c r="M35" s="122" t="n"/>
+      <c r="N35" s="122" t="n"/>
+      <c r="O35" s="122">
+        <f>M35*N35</f>
+        <v/>
+      </c>
+      <c r="P35" s="120" t="n"/>
+      <c r="Q35" s="123">
+        <f>G35-O35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" hidden="1" ht="16" customHeight="1">
+      <c r="B36" s="97" t="n"/>
+      <c r="C36" s="109" t="n"/>
+      <c r="D36" s="99" t="n"/>
+      <c r="E36" s="108" t="n"/>
+      <c r="F36" s="108" t="n"/>
+      <c r="G36" s="108" t="n"/>
+      <c r="H36" s="109" t="n"/>
+      <c r="I36" s="110" t="n"/>
+      <c r="J36" s="120" t="n"/>
+      <c r="K36" s="120" t="n"/>
+      <c r="L36" s="120" t="n"/>
+      <c r="M36" s="122" t="n"/>
+      <c r="N36" s="122" t="n"/>
+      <c r="O36" s="122" t="n"/>
+      <c r="P36" s="120" t="n"/>
+      <c r="Q36" s="123" t="n"/>
+    </row>
+    <row r="37" hidden="1" ht="16" customHeight="1">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>⑩</t>
+        </is>
+      </c>
+      <c r="C37" s="57" t="n"/>
+      <c r="D37" s="111" t="n"/>
+      <c r="E37" s="121" t="n"/>
+      <c r="F37" s="121">
+        <f>ROUNDUP(N37*$M$17,-3)</f>
+        <v/>
+      </c>
+      <c r="G37" s="121">
+        <f>E37*F37</f>
+        <v/>
+      </c>
+      <c r="H37" s="112" t="n"/>
+      <c r="I37" s="113" t="n"/>
+      <c r="J37" s="120" t="n"/>
+      <c r="K37" s="120" t="n"/>
+      <c r="L37" s="120" t="n"/>
+      <c r="M37" s="122" t="n"/>
+      <c r="N37" s="122" t="n"/>
+      <c r="O37" s="122">
+        <f>M37*N37</f>
+        <v/>
+      </c>
+      <c r="P37" s="120" t="n"/>
+      <c r="Q37" s="123">
+        <f>G37-O37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" hidden="1" ht="16" customHeight="1">
+      <c r="B38" s="97" t="n"/>
+      <c r="C38" s="109" t="n"/>
+      <c r="D38" s="99" t="n"/>
+      <c r="E38" s="108" t="n"/>
+      <c r="F38" s="108" t="n"/>
+      <c r="G38" s="108" t="n"/>
+      <c r="H38" s="109" t="n"/>
+      <c r="I38" s="110" t="n"/>
+      <c r="J38" s="120" t="n"/>
+      <c r="K38" s="120" t="n"/>
+      <c r="L38" s="120" t="n"/>
+      <c r="M38" s="122" t="n"/>
+      <c r="N38" s="122" t="n"/>
+      <c r="O38" s="122" t="n"/>
+      <c r="P38" s="120" t="n"/>
+      <c r="Q38" s="123" t="n"/>
+    </row>
+    <row r="39" hidden="1" ht="16" customHeight="1">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>⑪</t>
+        </is>
+      </c>
+      <c r="C39" s="57" t="n"/>
+      <c r="D39" s="111" t="n"/>
+      <c r="E39" s="121" t="n"/>
+      <c r="F39" s="121">
+        <f>ROUNDUP(N39*$M$17,-3)</f>
+        <v/>
+      </c>
+      <c r="G39" s="121">
+        <f>E39*F39</f>
+        <v/>
+      </c>
+      <c r="H39" s="112" t="n"/>
+      <c r="I39" s="113" t="n"/>
+      <c r="J39" s="120" t="n"/>
+      <c r="K39" s="120" t="n"/>
+      <c r="L39" s="120" t="n"/>
+      <c r="M39" s="122" t="n"/>
+      <c r="N39" s="122" t="n"/>
+      <c r="O39" s="122">
+        <f>M39*N39</f>
+        <v/>
+      </c>
+      <c r="P39" s="120" t="n"/>
+      <c r="Q39" s="123">
+        <f>G39-O39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" hidden="1" ht="16" customHeight="1">
+      <c r="B40" s="97" t="n"/>
+      <c r="C40" s="109" t="n"/>
+      <c r="D40" s="99" t="n"/>
+      <c r="E40" s="108" t="n"/>
+      <c r="F40" s="108" t="n"/>
+      <c r="G40" s="108" t="n"/>
+      <c r="H40" s="109" t="n"/>
+      <c r="I40" s="110" t="n"/>
+      <c r="J40" s="120" t="n"/>
+      <c r="K40" s="120" t="n"/>
+      <c r="L40" s="120" t="n"/>
+      <c r="M40" s="122" t="n"/>
+      <c r="N40" s="122" t="n"/>
+      <c r="O40" s="122" t="n"/>
+      <c r="P40" s="120" t="n"/>
+      <c r="Q40" s="123" t="n"/>
+    </row>
+    <row r="41" hidden="1" ht="16" customHeight="1">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>⑫</t>
+        </is>
+      </c>
+      <c r="C41" s="57" t="n"/>
+      <c r="D41" s="111" t="n"/>
+      <c r="E41" s="121" t="n"/>
+      <c r="F41" s="121">
+        <f>ROUNDUP(N41*$M$17,-3)</f>
+        <v/>
+      </c>
+      <c r="G41" s="121">
+        <f>E41*F41</f>
+        <v/>
+      </c>
+      <c r="H41" s="112" t="n"/>
+      <c r="I41" s="113" t="n"/>
+      <c r="J41" s="120" t="n"/>
+      <c r="K41" s="120" t="n"/>
+      <c r="L41" s="120" t="n"/>
+      <c r="M41" s="122" t="n"/>
+      <c r="N41" s="122" t="n"/>
+      <c r="O41" s="122">
+        <f>M41*N41</f>
+        <v/>
+      </c>
+      <c r="P41" s="120" t="n"/>
+      <c r="Q41" s="123">
+        <f>G41-O41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" hidden="1" ht="16" customHeight="1">
+      <c r="B42" s="97" t="n"/>
+      <c r="C42" s="109" t="n"/>
+      <c r="D42" s="99" t="n"/>
+      <c r="E42" s="108" t="n"/>
+      <c r="F42" s="108" t="n"/>
+      <c r="G42" s="108" t="n"/>
+      <c r="H42" s="109" t="n"/>
+      <c r="I42" s="110" t="n"/>
+      <c r="J42" s="120" t="n"/>
+      <c r="K42" s="120" t="n"/>
+      <c r="L42" s="120" t="n"/>
+      <c r="M42" s="122" t="n"/>
+      <c r="N42" s="122" t="n"/>
+      <c r="O42" s="122" t="n"/>
+      <c r="P42" s="120" t="n"/>
+      <c r="Q42" s="123" t="n"/>
+    </row>
+    <row r="43" hidden="1" ht="16" customHeight="1">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>⑬</t>
+        </is>
+      </c>
+      <c r="C43" s="57" t="n"/>
+      <c r="D43" s="111" t="n"/>
+      <c r="E43" s="121" t="n"/>
+      <c r="F43" s="121">
+        <f>ROUNDUP(N43*$M$17,-3)</f>
+        <v/>
+      </c>
+      <c r="G43" s="121">
+        <f>E43*F43</f>
+        <v/>
+      </c>
+      <c r="H43" s="112" t="n"/>
+      <c r="I43" s="113" t="n"/>
+      <c r="J43" s="120" t="n"/>
+      <c r="K43" s="120" t="n"/>
+      <c r="L43" s="120" t="n"/>
+      <c r="M43" s="122" t="n"/>
+      <c r="N43" s="122" t="n"/>
+      <c r="O43" s="122">
+        <f>M43*N43</f>
+        <v/>
+      </c>
+      <c r="P43" s="120" t="n"/>
+      <c r="Q43" s="123">
+        <f>G43-O43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" hidden="1" ht="16" customHeight="1">
+      <c r="B44" s="97" t="n"/>
+      <c r="C44" s="109" t="n"/>
+      <c r="D44" s="99" t="n"/>
+      <c r="E44" s="108" t="n"/>
+      <c r="F44" s="108" t="n"/>
+      <c r="G44" s="108" t="n"/>
+      <c r="H44" s="109" t="n"/>
+      <c r="I44" s="110" t="n"/>
+      <c r="J44" s="120" t="n"/>
+      <c r="K44" s="120" t="n"/>
+      <c r="L44" s="120" t="n"/>
+      <c r="M44" s="122" t="n"/>
+      <c r="N44" s="122" t="n"/>
+      <c r="O44" s="122" t="n"/>
+      <c r="P44" s="120" t="n"/>
+      <c r="Q44" s="123" t="n"/>
+    </row>
+    <row r="45" hidden="1" ht="16" customHeight="1">
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>⑭</t>
+        </is>
+      </c>
+      <c r="C45" s="57" t="n"/>
+      <c r="D45" s="111" t="n"/>
+      <c r="E45" s="121" t="n"/>
+      <c r="F45" s="121">
+        <f>ROUNDUP(N45*$M$17,-3)</f>
+        <v/>
+      </c>
+      <c r="G45" s="121">
+        <f>E45*F45</f>
+        <v/>
+      </c>
+      <c r="H45" s="112" t="n"/>
+      <c r="I45" s="113" t="n"/>
+      <c r="J45" s="120" t="n"/>
+      <c r="K45" s="120" t="n"/>
+      <c r="L45" s="120" t="n"/>
+      <c r="M45" s="122" t="n"/>
+      <c r="N45" s="122" t="n"/>
+      <c r="O45" s="122">
+        <f>M45*N45</f>
+        <v/>
+      </c>
+      <c r="P45" s="120" t="n"/>
+      <c r="Q45" s="123">
+        <f>G45-O45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" hidden="1" ht="16.5" customHeight="1" thickBot="1">
+      <c r="B46" s="97" t="n"/>
+      <c r="C46" s="109" t="n"/>
+      <c r="D46" s="99" t="n"/>
+      <c r="E46" s="108" t="n"/>
+      <c r="F46" s="108" t="n"/>
+      <c r="G46" s="108" t="n"/>
+      <c r="H46" s="109" t="n"/>
+      <c r="I46" s="110" t="n"/>
+      <c r="J46" s="120" t="n"/>
+      <c r="K46" s="120" t="n"/>
+      <c r="L46" s="120" t="n"/>
+      <c r="M46" s="122" t="n"/>
+      <c r="N46" s="122" t="n"/>
+      <c r="O46" s="122" t="n"/>
+      <c r="P46" s="120" t="n"/>
+      <c r="Q46" s="123" t="n"/>
+    </row>
+    <row r="47" hidden="1">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>⑮</t>
+        </is>
+      </c>
+      <c r="C47" s="57" t="n"/>
+      <c r="D47" s="111" t="n"/>
+      <c r="E47" s="121" t="n"/>
+      <c r="F47" s="121">
+        <f>ROUNDUP(N47*$M$17,-3)</f>
+        <v/>
+      </c>
+      <c r="G47" s="121">
+        <f>E47*F47</f>
+        <v/>
+      </c>
+      <c r="H47" s="112" t="n"/>
+      <c r="I47" s="113" t="n"/>
+      <c r="J47" s="120" t="n"/>
+      <c r="K47" s="120" t="n"/>
+      <c r="L47" s="120" t="n"/>
+      <c r="M47" s="122" t="n"/>
+      <c r="N47" s="122" t="n"/>
+      <c r="O47" s="122">
+        <f>M47*N47</f>
+        <v/>
+      </c>
+      <c r="P47" s="120" t="n"/>
+      <c r="Q47" s="123">
+        <f>G47-O47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" hidden="1">
+      <c r="B48" s="97" t="n"/>
+      <c r="C48" s="109" t="n"/>
+      <c r="D48" s="99" t="n"/>
+      <c r="E48" s="108" t="n"/>
+      <c r="F48" s="108" t="n"/>
+      <c r="G48" s="108" t="n"/>
+      <c r="H48" s="109" t="n"/>
+      <c r="I48" s="110" t="n"/>
+      <c r="J48" s="120" t="n"/>
+      <c r="K48" s="120" t="n"/>
+      <c r="L48" s="120" t="n"/>
+      <c r="M48" s="122" t="n"/>
+      <c r="N48" s="122" t="n"/>
+      <c r="O48" s="122" t="n"/>
+      <c r="P48" s="120" t="n"/>
+      <c r="Q48" s="123" t="n"/>
+    </row>
+    <row r="49" hidden="1">
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>⑯</t>
+        </is>
+      </c>
+      <c r="C49" s="57" t="n"/>
+      <c r="D49" s="111" t="n"/>
+      <c r="E49" s="121" t="n"/>
+      <c r="F49" s="121">
+        <f>ROUNDUP(N49*$M$17,-3)</f>
+        <v/>
+      </c>
+      <c r="G49" s="121">
+        <f>E49*F49</f>
+        <v/>
+      </c>
+      <c r="H49" s="112" t="n"/>
+      <c r="I49" s="113" t="n"/>
+      <c r="J49" s="120" t="n"/>
+      <c r="K49" s="120" t="n"/>
+      <c r="L49" s="120" t="n"/>
+      <c r="M49" s="122" t="n"/>
+      <c r="N49" s="122" t="n"/>
+      <c r="O49" s="122">
+        <f>M49*N49</f>
+        <v/>
+      </c>
+      <c r="P49" s="120" t="n"/>
+      <c r="Q49" s="123">
+        <f>G49-O49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" hidden="1">
+      <c r="B50" s="97" t="n"/>
+      <c r="C50" s="109" t="n"/>
+      <c r="D50" s="99" t="n"/>
+      <c r="E50" s="108" t="n"/>
+      <c r="F50" s="108" t="n"/>
+      <c r="G50" s="108" t="n"/>
+      <c r="H50" s="109" t="n"/>
+      <c r="I50" s="110" t="n"/>
+      <c r="J50" s="120" t="n"/>
+      <c r="K50" s="120" t="n"/>
+      <c r="L50" s="120" t="n"/>
+      <c r="M50" s="122" t="n"/>
+      <c r="N50" s="122" t="n"/>
+      <c r="O50" s="122" t="n"/>
+      <c r="P50" s="120" t="n"/>
+      <c r="Q50" s="123" t="n"/>
+    </row>
+    <row r="51" hidden="1">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>⑰</t>
+        </is>
+      </c>
+      <c r="C51" s="57" t="n"/>
+      <c r="D51" s="111" t="n"/>
+      <c r="E51" s="121" t="n"/>
+      <c r="F51" s="121">
+        <f>ROUNDUP(N51*$M$17,-3)</f>
+        <v/>
+      </c>
+      <c r="G51" s="121">
+        <f>E51*F51</f>
+        <v/>
+      </c>
+      <c r="H51" s="112" t="n"/>
+      <c r="I51" s="113" t="n"/>
+      <c r="J51" s="120" t="n"/>
+      <c r="K51" s="120" t="n"/>
+      <c r="L51" s="120" t="n"/>
+      <c r="M51" s="122" t="n"/>
+      <c r="N51" s="122" t="n"/>
+      <c r="O51" s="122">
+        <f>M51*N51</f>
+        <v/>
+      </c>
+      <c r="P51" s="120" t="n"/>
+      <c r="Q51" s="123">
+        <f>G51-O51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" hidden="1">
+      <c r="B52" s="97" t="n"/>
+      <c r="C52" s="109" t="n"/>
+      <c r="D52" s="99" t="n"/>
+      <c r="E52" s="108" t="n"/>
+      <c r="F52" s="108" t="n"/>
+      <c r="G52" s="108" t="n"/>
+      <c r="H52" s="109" t="n"/>
+      <c r="I52" s="110" t="n"/>
+      <c r="J52" s="120" t="n"/>
+      <c r="K52" s="120" t="n"/>
+      <c r="L52" s="120" t="n"/>
+      <c r="M52" s="122" t="n"/>
+      <c r="N52" s="122" t="n"/>
+      <c r="O52" s="122" t="n"/>
+      <c r="P52" s="120" t="n"/>
+      <c r="Q52" s="123" t="n"/>
+    </row>
+    <row r="53" hidden="1">
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>⑱</t>
+        </is>
+      </c>
+      <c r="C53" s="45" t="inlineStr">
         <is>
           <t>運賃</t>
         </is>
       </c>
-      <c r="D25" s="92" t="n"/>
-      <c r="E25" s="15" t="n">
+      <c r="D53" s="92" t="n"/>
+      <c r="E53" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="28" t="n"/>
-      <c r="G25" s="28" t="n"/>
-      <c r="H25" s="112" t="n"/>
-      <c r="I25" s="114" t="n"/>
-      <c r="M25" s="41" t="n">
+      <c r="F53" s="28" t="n"/>
+      <c r="G53" s="28">
+        <f>E53*F53</f>
+        <v/>
+      </c>
+      <c r="H53" s="112" t="n"/>
+      <c r="I53" s="114" t="n"/>
+      <c r="J53" s="120" t="n"/>
+      <c r="K53" s="120" t="n"/>
+      <c r="L53" s="120" t="n"/>
+      <c r="M53" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="N25" s="41" t="n"/>
-      <c r="O25" s="41">
-        <f>M25*N25</f>
-        <v/>
-      </c>
-      <c r="P25" s="85" t="inlineStr">
+      <c r="N53" s="41" t="n"/>
+      <c r="O53" s="41">
+        <f>M53*N53</f>
+        <v/>
+      </c>
+      <c r="P53" s="85" t="inlineStr">
         <is>
           <t>運賃</t>
         </is>
       </c>
-      <c r="Q25" s="26">
-        <f>G25-O25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="13.75" customHeight="1" thickBot="1">
-      <c r="B26" s="21" t="n"/>
-      <c r="C26" s="86" t="n"/>
-      <c r="D26" s="115" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="Q53" s="26">
+        <f>G53-O53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="13.75" customHeight="1">
+      <c r="B54" s="21" t="n"/>
+      <c r="C54" s="86" t="n"/>
+      <c r="D54" s="115" t="n"/>
+      <c r="E54" s="16" t="n"/>
+      <c r="F54" s="14" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="G26" s="14">
-        <f>SUM(G19:G25)</f>
-        <v/>
-      </c>
-      <c r="H26" s="116" t="n"/>
-      <c r="I26" s="117" t="n"/>
-      <c r="Q26" s="35">
-        <f>SUM(Q19:Q25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1" thickBot="1" thickTop="1">
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="17" t="n"/>
-      <c r="G27" s="17" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="36" t="inlineStr">
+      <c r="G54" s="14">
+        <f>SUM(G19:G53)</f>
+        <v/>
+      </c>
+      <c r="H54" s="116" t="n"/>
+      <c r="I54" s="117" t="n"/>
+      <c r="J54" s="120" t="n"/>
+      <c r="K54" s="120" t="n"/>
+      <c r="L54" s="120" t="n"/>
+      <c r="M54" s="120" t="n"/>
+      <c r="N54" s="120" t="n"/>
+      <c r="O54" s="120" t="n"/>
+      <c r="P54" s="120" t="n"/>
+      <c r="Q54" s="35">
+        <f>SUM(Q19:Q53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="17" t="n"/>
+      <c r="F55" s="17" t="n"/>
+      <c r="G55" s="17" t="n"/>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="6" t="n"/>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="36" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="D28" s="29" t="n"/>
-      <c r="E28" s="18" t="n"/>
-      <c r="F28" s="18" t="n"/>
-      <c r="G28" s="18" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="9" t="n"/>
-    </row>
-    <row r="29" hidden="1" ht="16" customHeight="1">
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="31" t="n"/>
-      <c r="D29" s="29" t="n"/>
-      <c r="E29" s="34" t="n"/>
-      <c r="F29" s="34" t="n"/>
-      <c r="G29" s="34" t="n"/>
-      <c r="H29" s="29" t="n"/>
-      <c r="I29" s="11" t="n"/>
-    </row>
-    <row r="30" hidden="1" ht="16" customHeight="1">
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="29" t="n"/>
-      <c r="E30" s="34" t="n"/>
-      <c r="F30" s="34" t="n"/>
-      <c r="G30" s="34" t="n"/>
-      <c r="H30" s="29" t="n"/>
-      <c r="I30" s="11" t="n"/>
-    </row>
-    <row r="31" hidden="1" ht="16.25" customHeight="1" thickBot="1">
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="30" t="n"/>
-      <c r="D31" s="31" t="n"/>
-      <c r="E31" s="31" t="n"/>
-      <c r="F31" s="31" t="n"/>
-      <c r="G31" s="31" t="n"/>
-      <c r="H31" s="31" t="n"/>
-      <c r="I31" s="11" t="n"/>
-    </row>
-    <row r="32" hidden="1" ht="16.25" customHeight="1" thickBot="1">
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="32" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="31" t="n"/>
-      <c r="G32" s="31" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="11" t="n"/>
-    </row>
-    <row r="33" hidden="1" ht="16" customHeight="1">
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="32" t="n"/>
-      <c r="D33" s="33" t="n"/>
-      <c r="E33" s="33" t="n"/>
-      <c r="F33" s="34" t="n"/>
-      <c r="G33" s="34" t="n"/>
-      <c r="H33" s="29" t="n"/>
-      <c r="I33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="89" t="n"/>
-      <c r="D34" s="33" t="n"/>
-      <c r="E34" s="33" t="n"/>
-      <c r="F34" s="34" t="n"/>
-      <c r="G34" s="34" t="n"/>
-      <c r="H34" s="29" t="n"/>
-      <c r="I34" s="11" t="n"/>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="33" t="n"/>
-      <c r="E35" s="33" t="n"/>
-      <c r="F35" s="34" t="n"/>
-      <c r="G35" s="34" t="n"/>
-      <c r="H35" s="29" t="n"/>
-      <c r="I35" s="11" t="n"/>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="33" t="n"/>
-      <c r="E36" s="33" t="n"/>
-      <c r="F36" s="34" t="n"/>
-      <c r="G36" s="34" t="n"/>
-      <c r="H36" s="29" t="n"/>
-      <c r="I36" s="11" t="n"/>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="32" t="n"/>
-      <c r="D37" s="33" t="n"/>
-      <c r="E37" s="33" t="n"/>
-      <c r="F37" s="34" t="n"/>
-      <c r="G37" s="34" t="n"/>
-      <c r="H37" s="29" t="n"/>
-      <c r="I37" s="11" t="n"/>
-    </row>
-    <row r="38" hidden="1" ht="16" customHeight="1">
-      <c r="B38" s="10" t="n"/>
-      <c r="D38" s="33" t="n"/>
-      <c r="E38" s="33" t="n"/>
-      <c r="F38" s="34" t="n"/>
-      <c r="G38" s="34" t="n"/>
-      <c r="H38" s="29" t="n"/>
-      <c r="I38" s="11" t="n"/>
-    </row>
-    <row r="39" hidden="1" ht="16" customHeight="1">
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="32" t="n"/>
-      <c r="D39" s="33" t="n"/>
-      <c r="E39" s="33" t="n"/>
-      <c r="F39" s="34" t="n"/>
-      <c r="G39" s="34" t="n"/>
-      <c r="H39" s="29" t="n"/>
-      <c r="I39" s="11" t="n"/>
-    </row>
-    <row r="40" hidden="1" ht="16" customHeight="1">
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="32" t="n"/>
-      <c r="D40" s="33" t="n"/>
-      <c r="E40" s="33" t="n"/>
-      <c r="F40" s="34" t="n"/>
-      <c r="G40" s="34" t="n"/>
-      <c r="H40" s="29" t="n"/>
-      <c r="I40" s="11" t="n"/>
-    </row>
-    <row r="41" hidden="1" ht="16" customHeight="1">
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="32" t="n"/>
-      <c r="D41" s="33" t="n"/>
-      <c r="E41" s="33" t="n"/>
-      <c r="F41" s="34" t="n"/>
-      <c r="G41" s="34" t="n"/>
-      <c r="H41" s="29" t="n"/>
-      <c r="I41" s="11" t="n"/>
-    </row>
-    <row r="42" hidden="1" ht="16" customHeight="1">
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="32" t="n"/>
-      <c r="D42" s="33" t="n"/>
-      <c r="E42" s="33" t="n"/>
-      <c r="F42" s="34" t="n"/>
-      <c r="G42" s="34" t="n"/>
-      <c r="H42" s="29" t="n"/>
-      <c r="I42" s="11" t="n"/>
-    </row>
-    <row r="43" hidden="1" ht="16" customHeight="1">
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="32" t="n"/>
-      <c r="D43" s="33" t="n"/>
-      <c r="E43" s="33" t="n"/>
-      <c r="F43" s="34" t="n"/>
-      <c r="G43" s="34" t="n"/>
-      <c r="H43" s="29" t="n"/>
-      <c r="I43" s="11" t="n"/>
-    </row>
-    <row r="44" hidden="1" ht="16" customHeight="1">
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="32" t="n"/>
-      <c r="D44" s="33" t="n"/>
-      <c r="E44" s="33" t="n"/>
-      <c r="F44" s="34" t="n"/>
-      <c r="G44" s="34" t="n"/>
-      <c r="H44" s="29" t="n"/>
-      <c r="I44" s="11" t="n"/>
-    </row>
-    <row r="45" hidden="1" ht="16" customHeight="1">
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="32" t="n"/>
-      <c r="D45" s="33" t="n"/>
-      <c r="E45" s="33" t="n"/>
-      <c r="F45" s="34" t="n"/>
-      <c r="G45" s="34" t="n"/>
-      <c r="H45" s="29" t="n"/>
-      <c r="I45" s="11" t="n"/>
-    </row>
-    <row r="46" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="42" t="n"/>
-      <c r="D46" s="23" t="n"/>
-      <c r="E46" s="23" t="n"/>
-      <c r="F46" s="50" t="n"/>
-      <c r="G46" s="90" t="n"/>
-      <c r="H46" s="90" t="n"/>
-      <c r="I46" s="102" t="n"/>
+      <c r="D56" s="29" t="n"/>
+      <c r="E56" s="18" t="n"/>
+      <c r="F56" s="18" t="n"/>
+      <c r="G56" s="18" t="n"/>
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="9" t="n"/>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="31" t="n"/>
+      <c r="D57" s="29" t="n"/>
+      <c r="E57" s="34" t="n"/>
+      <c r="F57" s="34" t="n"/>
+      <c r="G57" s="34" t="n"/>
+      <c r="H57" s="29" t="n"/>
+      <c r="I57" s="11" t="n"/>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="31" t="n"/>
+      <c r="D58" s="29" t="n"/>
+      <c r="E58" s="34" t="n"/>
+      <c r="F58" s="34" t="n"/>
+      <c r="G58" s="34" t="n"/>
+      <c r="H58" s="29" t="n"/>
+      <c r="I58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="30" t="n"/>
+      <c r="D59" s="31" t="n"/>
+      <c r="E59" s="31" t="n"/>
+      <c r="F59" s="31" t="n"/>
+      <c r="G59" s="31" t="n"/>
+      <c r="H59" s="31" t="n"/>
+      <c r="I59" s="11" t="n"/>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="32" t="n"/>
+      <c r="D60" s="31" t="n"/>
+      <c r="E60" s="31" t="n"/>
+      <c r="F60" s="31" t="n"/>
+      <c r="G60" s="31" t="n"/>
+      <c r="H60" s="31" t="n"/>
+      <c r="I60" s="11" t="n"/>
+    </row>
+    <row r="61" hidden="1" ht="16" customHeight="1">
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="32" t="n"/>
+      <c r="D61" s="33" t="n"/>
+      <c r="E61" s="33" t="n"/>
+      <c r="F61" s="34" t="n"/>
+      <c r="G61" s="34" t="n"/>
+      <c r="H61" s="29" t="n"/>
+      <c r="I61" s="11" t="n"/>
+    </row>
+    <row r="62" hidden="1" ht="16" customHeight="1">
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="89" t="n"/>
+      <c r="D62" s="33" t="n"/>
+      <c r="E62" s="33" t="n"/>
+      <c r="F62" s="34" t="n"/>
+      <c r="G62" s="34" t="n"/>
+      <c r="H62" s="29" t="n"/>
+      <c r="I62" s="11" t="n"/>
+    </row>
+    <row r="63" hidden="1" ht="16" customHeight="1">
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="31" t="n"/>
+      <c r="D63" s="33" t="n"/>
+      <c r="E63" s="33" t="n"/>
+      <c r="F63" s="34" t="n"/>
+      <c r="G63" s="34" t="n"/>
+      <c r="H63" s="29" t="n"/>
+      <c r="I63" s="11" t="n"/>
+    </row>
+    <row r="64" hidden="1" ht="16" customHeight="1">
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="31" t="n"/>
+      <c r="D64" s="33" t="n"/>
+      <c r="E64" s="33" t="n"/>
+      <c r="F64" s="34" t="n"/>
+      <c r="G64" s="34" t="n"/>
+      <c r="H64" s="29" t="n"/>
+      <c r="I64" s="11" t="n"/>
+    </row>
+    <row r="65" hidden="1" ht="16" customHeight="1">
+      <c r="B65" s="10" t="n"/>
+      <c r="C65" s="32" t="n"/>
+      <c r="D65" s="33" t="n"/>
+      <c r="E65" s="33" t="n"/>
+      <c r="F65" s="34" t="n"/>
+      <c r="G65" s="34" t="n"/>
+      <c r="H65" s="29" t="n"/>
+      <c r="I65" s="11" t="n"/>
+    </row>
+    <row r="66" hidden="1" ht="16" customHeight="1">
+      <c r="B66" s="10" t="n"/>
+      <c r="D66" s="33" t="n"/>
+      <c r="E66" s="33" t="n"/>
+      <c r="F66" s="34" t="n"/>
+      <c r="G66" s="34" t="n"/>
+      <c r="H66" s="29" t="n"/>
+      <c r="I66" s="11" t="n"/>
+    </row>
+    <row r="67" hidden="1" ht="16" customHeight="1">
+      <c r="B67" s="10" t="n"/>
+      <c r="C67" s="32" t="n"/>
+      <c r="D67" s="33" t="n"/>
+      <c r="E67" s="33" t="n"/>
+      <c r="F67" s="34" t="n"/>
+      <c r="G67" s="34" t="n"/>
+      <c r="H67" s="29" t="n"/>
+      <c r="I67" s="11" t="n"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="10" t="n"/>
+      <c r="C68" s="32" t="n"/>
+      <c r="D68" s="33" t="n"/>
+      <c r="E68" s="33" t="n"/>
+      <c r="F68" s="34" t="n"/>
+      <c r="G68" s="34" t="n"/>
+      <c r="H68" s="29" t="n"/>
+      <c r="I68" s="11" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="32" t="n"/>
+      <c r="D69" s="33" t="n"/>
+      <c r="E69" s="33" t="n"/>
+      <c r="F69" s="34" t="n"/>
+      <c r="G69" s="34" t="n"/>
+      <c r="H69" s="29" t="n"/>
+      <c r="I69" s="11" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="32" t="n"/>
+      <c r="D70" s="33" t="n"/>
+      <c r="E70" s="33" t="n"/>
+      <c r="F70" s="34" t="n"/>
+      <c r="G70" s="34" t="n"/>
+      <c r="H70" s="29" t="n"/>
+      <c r="I70" s="11" t="n"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="10" t="n"/>
+      <c r="C71" s="32" t="n"/>
+      <c r="D71" s="33" t="n"/>
+      <c r="E71" s="33" t="n"/>
+      <c r="F71" s="34" t="n"/>
+      <c r="G71" s="34" t="n"/>
+      <c r="H71" s="29" t="n"/>
+      <c r="I71" s="11" t="n"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="32" t="n"/>
+      <c r="D72" s="33" t="n"/>
+      <c r="E72" s="33" t="n"/>
+      <c r="F72" s="34" t="n"/>
+      <c r="G72" s="34" t="n"/>
+      <c r="H72" s="29" t="n"/>
+      <c r="I72" s="11" t="n"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="32" t="n"/>
+      <c r="D73" s="33" t="n"/>
+      <c r="E73" s="33" t="n"/>
+      <c r="F73" s="34" t="n"/>
+      <c r="G73" s="34" t="n"/>
+      <c r="H73" s="29" t="n"/>
+      <c r="I73" s="11" t="n"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="42" t="n"/>
+      <c r="D74" s="23" t="n"/>
+      <c r="E74" s="23" t="n"/>
+      <c r="F74" s="50" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="121">
+    <mergeCell ref="C47:D48"/>
     <mergeCell ref="H17:I18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="H6:I11"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C31:D32"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="E23:E24"/>
     <mergeCell ref="C23:D24"/>
-    <mergeCell ref="E19:E20"/>
     <mergeCell ref="H19:I20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C51:D52"/>
     <mergeCell ref="B23:B24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="H23:I24"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="H29:I30"/>
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="E25:E26"/>
     <mergeCell ref="H21:I22"/>
     <mergeCell ref="E21:E22"/>
     <mergeCell ref="G21:G22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="H31:I32"/>
+    <mergeCell ref="C35:D36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="H51:I52"/>
+    <mergeCell ref="H6:I11"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="C39:D40"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="H33:I34"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H35:I36"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="H39:I40"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="H45:I46"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="C43:D44"/>
+    <mergeCell ref="H47:I48"/>
+    <mergeCell ref="H27:I28"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="H37:I38"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="C37:D38"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="H25:I26"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="H41:I42"/>
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="H23:I24"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="H43:I44"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="E37:E38"/>
     <mergeCell ref="C13:D13"/>
-    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="H49:I50"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="H26:I26"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0.1968503937007874" top="1.062992125984252" bottom="0.984251968503937" header="0.5118110236220472" footer="0.5118110236220472"/>

--- a/quote_automation/assets/base_quote_template.xlsx
+++ b/quote_automation/assets/base_quote_template.xlsx
@@ -758,7 +758,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1086,6 +1086,9 @@
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="B1:Q74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3.08984375" customWidth="1" style="1" min="1" max="1"/>
@@ -2314,7 +2317,7 @@
       <c r="F10" s="39" t="n"/>
     </row>
     <row r="11" ht="17.25" customHeight="1">
-      <c r="C11" s="73" t="inlineStr">
+      <c r="C11" s="124" t="inlineStr">
         <is>
           <t>受渡場所　及び条件　：貴社車上渡し</t>
         </is>
@@ -2324,7 +2327,7 @@
       <c r="F11" s="39" t="n"/>
     </row>
     <row r="12" ht="17.25" customHeight="1">
-      <c r="C12" s="73" t="inlineStr">
+      <c r="C12" s="124" t="inlineStr">
         <is>
           <t>決済条件               ：従来通り</t>
         </is>
@@ -2344,7 +2347,7 @@
       <c r="I13" s="12" t="n"/>
     </row>
     <row r="14" ht="17.25" customHeight="1">
-      <c r="C14" s="73" t="inlineStr">
+      <c r="C14" s="124" t="inlineStr">
         <is>
           <t>備考：運賃込み価格</t>
         </is>

--- a/quote_automation/assets/base_quote_template.xlsx
+++ b/quote_automation/assets/base_quote_template.xlsx
@@ -109,7 +109,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="53">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -751,6 +751,7 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -758,7 +759,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1089,6 +1090,31 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="38" fontId="8" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1468,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:Q74"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3.08984375" customWidth="1" style="1" min="1" max="1"/>
@@ -3522,71 +3548,88 @@
       <c r="I67" s="11" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="10" t="n"/>
-      <c r="C68" s="32" t="n"/>
-      <c r="D68" s="33" t="n"/>
-      <c r="E68" s="33" t="n"/>
-      <c r="F68" s="34" t="n"/>
-      <c r="G68" s="34" t="n"/>
-      <c r="H68" s="29" t="n"/>
-      <c r="I68" s="11" t="n"/>
+      <c r="A68" s="125" t="n"/>
+      <c r="B68" s="126" t="n"/>
+      <c r="C68" s="127" t="n"/>
+      <c r="D68" s="128" t="n"/>
+      <c r="E68" s="128" t="n"/>
+      <c r="F68" s="129" t="n"/>
+      <c r="G68" s="129" t="n"/>
+      <c r="H68" s="130" t="n"/>
+      <c r="I68" s="130" t="n"/>
+      <c r="J68" s="125" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="10" t="n"/>
-      <c r="C69" s="32" t="n"/>
-      <c r="D69" s="33" t="n"/>
-      <c r="E69" s="33" t="n"/>
-      <c r="F69" s="34" t="n"/>
-      <c r="G69" s="34" t="n"/>
-      <c r="H69" s="29" t="n"/>
-      <c r="I69" s="11" t="n"/>
+      <c r="A69" s="125" t="n"/>
+      <c r="B69" s="126" t="n"/>
+      <c r="C69" s="127" t="n"/>
+      <c r="D69" s="128" t="n"/>
+      <c r="E69" s="128" t="n"/>
+      <c r="F69" s="129" t="n"/>
+      <c r="G69" s="129" t="n"/>
+      <c r="H69" s="130" t="n"/>
+      <c r="I69" s="130" t="n"/>
+      <c r="J69" s="125" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="10" t="n"/>
-      <c r="C70" s="32" t="n"/>
-      <c r="D70" s="33" t="n"/>
-      <c r="E70" s="33" t="n"/>
-      <c r="F70" s="34" t="n"/>
-      <c r="G70" s="34" t="n"/>
-      <c r="H70" s="29" t="n"/>
-      <c r="I70" s="11" t="n"/>
+      <c r="A70" s="125" t="n"/>
+      <c r="B70" s="126" t="n"/>
+      <c r="C70" s="127" t="n"/>
+      <c r="D70" s="128" t="n"/>
+      <c r="E70" s="128" t="n"/>
+      <c r="F70" s="129" t="n"/>
+      <c r="G70" s="129" t="n"/>
+      <c r="H70" s="130" t="n"/>
+      <c r="I70" s="130" t="n"/>
+      <c r="J70" s="125" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="10" t="n"/>
-      <c r="C71" s="32" t="n"/>
-      <c r="D71" s="33" t="n"/>
-      <c r="E71" s="33" t="n"/>
-      <c r="F71" s="34" t="n"/>
-      <c r="G71" s="34" t="n"/>
-      <c r="H71" s="29" t="n"/>
-      <c r="I71" s="11" t="n"/>
+      <c r="A71" s="125" t="n"/>
+      <c r="B71" s="126" t="n"/>
+      <c r="C71" s="127" t="n"/>
+      <c r="D71" s="128" t="n"/>
+      <c r="E71" s="128" t="n"/>
+      <c r="F71" s="129" t="n"/>
+      <c r="G71" s="129" t="n"/>
+      <c r="H71" s="130" t="n"/>
+      <c r="I71" s="130" t="n"/>
+      <c r="J71" s="125" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="10" t="n"/>
-      <c r="C72" s="32" t="n"/>
-      <c r="D72" s="33" t="n"/>
-      <c r="E72" s="33" t="n"/>
-      <c r="F72" s="34" t="n"/>
-      <c r="G72" s="34" t="n"/>
-      <c r="H72" s="29" t="n"/>
-      <c r="I72" s="11" t="n"/>
+      <c r="A72" s="125" t="n"/>
+      <c r="B72" s="126" t="n"/>
+      <c r="C72" s="127" t="n"/>
+      <c r="D72" s="128" t="n"/>
+      <c r="E72" s="128" t="n"/>
+      <c r="F72" s="129" t="n"/>
+      <c r="G72" s="129" t="n"/>
+      <c r="H72" s="130" t="n"/>
+      <c r="I72" s="130" t="n"/>
+      <c r="J72" s="125" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="10" t="n"/>
-      <c r="C73" s="32" t="n"/>
-      <c r="D73" s="33" t="n"/>
-      <c r="E73" s="33" t="n"/>
-      <c r="F73" s="34" t="n"/>
-      <c r="G73" s="34" t="n"/>
-      <c r="H73" s="29" t="n"/>
-      <c r="I73" s="11" t="n"/>
+      <c r="A73" s="125" t="n"/>
+      <c r="B73" s="126" t="n"/>
+      <c r="C73" s="127" t="n"/>
+      <c r="D73" s="128" t="n"/>
+      <c r="E73" s="128" t="n"/>
+      <c r="F73" s="129" t="n"/>
+      <c r="G73" s="129" t="n"/>
+      <c r="H73" s="130" t="n"/>
+      <c r="I73" s="130" t="n"/>
+      <c r="J73" s="125" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="5" t="n"/>
-      <c r="C74" s="42" t="n"/>
-      <c r="D74" s="23" t="n"/>
-      <c r="E74" s="23" t="n"/>
-      <c r="F74" s="50" t="n"/>
+      <c r="A74" s="125" t="n"/>
+      <c r="B74" s="126" t="n"/>
+      <c r="C74" s="131" t="n"/>
+      <c r="D74" s="132" t="n"/>
+      <c r="E74" s="132" t="n"/>
+      <c r="F74" s="133" t="n"/>
+      <c r="G74" s="125" t="n"/>
+      <c r="H74" s="125" t="n"/>
+      <c r="I74" s="125" t="n"/>
+      <c r="J74" s="125" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="121">

--- a/quote_automation/assets/base_quote_template.xlsx
+++ b/quote_automation/assets/base_quote_template.xlsx
@@ -759,7 +759,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1115,6 +1115,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2293,6 +2296,9 @@
         <v/>
       </c>
     </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="H4" s="134" t="n"/>
+    </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="C5" s="1" t="inlineStr">
         <is>
@@ -3632,7 +3638,7 @@
       <c r="J74" s="125" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="121">
+  <mergeCells count="122">
     <mergeCell ref="C47:D48"/>
     <mergeCell ref="H17:I18"/>
     <mergeCell ref="H53:I53"/>
@@ -3728,6 +3734,7 @@
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="F25:F26"/>
     <mergeCell ref="E33:E34"/>
+    <mergeCell ref="H4:I4"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="G19:G20"/>
     <mergeCell ref="C17:D18"/>

--- a/quote_automation/assets/base_quote_template.xlsx
+++ b/quote_automation/assets/base_quote_template.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
     <numFmt numFmtId="165" formatCode="[$-411]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
@@ -100,6 +100,11 @@
       <color rgb="FFFF0000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <charset val="128"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -759,7 +764,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1118,6 +1123,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2326,9 +2340,9 @@
     <row r="7" ht="17.25" customHeight="1"/>
     <row r="8" ht="17.25" customHeight="1">
       <c r="B8" s="2" t="n"/>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>総計金額：￥</t>
+      <c r="C8" s="137" t="inlineStr">
+        <is>
+          <t>総計金額（税抜）：￥</t>
         </is>
       </c>
       <c r="D8" s="38">
@@ -2337,7 +2351,17 @@
       </c>
       <c r="E8" s="22" t="n"/>
     </row>
-    <row r="9" ht="17.25" customHeight="1"/>
+    <row r="9" ht="17.25" customHeight="1">
+      <c r="C9" s="135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（税込10%）：￥</t>
+        </is>
+      </c>
+      <c r="D9" s="136">
+        <f>ROUND(D8*1.1,0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="10" ht="17.25" customHeight="1">
       <c r="C10" s="2" t="inlineStr">
         <is>

--- a/quote_automation/assets/base_quote_template.xlsx
+++ b/quote_automation/assets/base_quote_template.xlsx
@@ -1525,8 +1525,8 @@
     <col width="10.36328125" customWidth="1" style="1" min="9" max="9"/>
     <col width="2.81640625" customWidth="1" style="1" min="10" max="10"/>
     <col width="8.90625" customWidth="1" style="1" min="11" max="12"/>
-    <col width="9" bestFit="1" customWidth="1" style="22" min="13" max="13"/>
-    <col width="9.90625" bestFit="1" customWidth="1" style="22" min="14" max="14"/>
+    <col hidden="1" width="9" bestFit="1" customWidth="1" style="22" min="13" max="13"/>
+    <col hidden="1" width="9.90625" bestFit="1" customWidth="1" style="22" min="14" max="14"/>
     <col width="11.90625" bestFit="1" customWidth="1" style="22" min="15" max="15"/>
     <col width="8.90625" customWidth="1" style="1" min="16" max="16"/>
     <col width="14.36328125" bestFit="1" customWidth="1" style="1" min="17" max="17"/>
